--- a/Unity/Assets/Config/Excel/GemTalentConfig.xlsx
+++ b/Unity/Assets/Config/Excel/GemTalentConfig.xlsx
@@ -37,7 +37,7 @@
     <author>作者</author>
   </authors>
   <commentList>
-    <comment ref="H4" authorId="0">
+    <comment ref="I4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="30">
   <si>
     <t>##var</t>
   </si>
@@ -87,6 +87,9 @@
   </si>
   <si>
     <t>CostPoint</t>
+  </si>
+  <si>
+    <t>AddPropreType</t>
   </si>
   <si>
     <t>Des</t>
@@ -125,6 +128,9 @@
     <t>激活消耗点数</t>
   </si>
   <si>
+    <t>效果类型</t>
+  </si>
+  <si>
     <t>描述</t>
   </si>
   <si>
@@ -134,10 +140,16 @@
     <t>火</t>
   </si>
   <si>
+    <t>攻击力+1%</t>
+  </si>
+  <si>
     <t>RolePropertyAdd;100402;0.01</t>
   </si>
   <si>
     <t>攻</t>
+  </si>
+  <si>
+    <t>技能：裂地击范围+1</t>
   </si>
   <si>
     <t>风</t>
@@ -8663,7 +8675,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -8676,6 +8688,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -11370,7 +11385,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2">
-    <tableStyle name="MySqlDefault" count="2" xr9:uid="{6E0B5B33-0F09-4A26-B2E3-3C21FF1B6471}">
+    <tableStyle name="MySqlDefault" count="2" xr9:uid="{A70C1D21-ECD7-4A90-9A27-70A3A888C662}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -11670,19 +11685,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <dimension ref="A1:I19"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="11" customWidth="1"/>
     <col min="4" max="4" width="11.625" customWidth="1"/>
     <col min="5" max="5" width="10.875" customWidth="1"/>
-    <col min="6" max="6" width="14.75" customWidth="1"/>
-    <col min="7" max="7" width="51.875" customWidth="1"/>
-    <col min="8" max="8" width="58.5" customWidth="1"/>
+    <col min="6" max="7" width="14.75" customWidth="1"/>
+    <col min="8" max="8" width="51.875" customWidth="1"/>
+    <col min="9" max="9" width="58.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:8">
+    <row r="1" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:9">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -11701,371 +11716,478 @@
       <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="5" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:8">
+    <row r="2" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:9">
       <c r="A2" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="7" t="s">
+      <c r="C2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="7" t="s">
+      <c r="D2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="E2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="8" t="s">
         <v>10</v>
       </c>
+      <c r="G2" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:8">
+    <row r="3" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:9">
       <c r="A3" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3" s="4"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" s="5"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="5"/>
     </row>
-    <row r="4" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:8">
+    <row r="4" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:9">
       <c r="A4" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="7" t="s">
+      <c r="C4" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="7" t="s">
+      <c r="E4" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="F4" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="G4" s="8" t="s">
         <v>19</v>
       </c>
+      <c r="H4" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="5" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:8">
-      <c r="B5" s="8">
+    <row r="5" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:9">
+      <c r="B5" s="9">
         <v>11001</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="8">
+      <c r="C5" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="9">
         <v>10001</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="9">
         <v>1</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="9">
         <v>25</v>
       </c>
-      <c r="G5" s="9"/>
+      <c r="G5" s="9">
+        <v>0</v>
+      </c>
       <c r="H5" s="10" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="6" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:8">
-      <c r="B6" s="8">
+    <row r="6" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:9">
+      <c r="B6" s="9">
         <v>11002</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="9">
+        <v>10002</v>
+      </c>
+      <c r="E6" s="9">
+        <v>1</v>
+      </c>
+      <c r="F6" s="9">
+        <v>25</v>
+      </c>
+      <c r="G6" s="9">
+        <v>1</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" s="11"/>
+    </row>
+    <row r="7" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:9">
+      <c r="B7" s="9">
+        <v>11003</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="9">
+        <v>10003</v>
+      </c>
+      <c r="E7" s="9">
+        <v>1</v>
+      </c>
+      <c r="F7" s="9">
+        <v>25</v>
+      </c>
+      <c r="G7" s="9">
+        <v>0</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:9">
+      <c r="B8" s="9">
+        <v>11004</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="9">
+        <v>10004</v>
+      </c>
+      <c r="E8" s="9">
+        <v>1</v>
+      </c>
+      <c r="F8" s="9">
+        <v>25</v>
+      </c>
+      <c r="G8" s="9">
+        <v>0</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:9">
+      <c r="B9" s="9">
+        <v>11005</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="9">
+        <v>10005</v>
+      </c>
+      <c r="E9" s="9">
+        <v>1</v>
+      </c>
+      <c r="F9" s="9">
+        <v>25</v>
+      </c>
+      <c r="G9" s="9">
+        <v>0</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:9">
+      <c r="B10" s="9">
+        <v>12001</v>
+      </c>
+      <c r="C10" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D10" s="9">
+        <v>10001</v>
+      </c>
+      <c r="E10" s="9">
+        <v>2</v>
+      </c>
+      <c r="F10" s="9">
+        <v>25</v>
+      </c>
+      <c r="G10" s="9">
+        <v>0</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:9">
+      <c r="B11" s="9">
+        <v>12002</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="9">
         <v>10002</v>
       </c>
-      <c r="E6" s="8">
-        <v>1</v>
-      </c>
-      <c r="F6" s="8">
+      <c r="E11" s="9">
+        <v>2</v>
+      </c>
+      <c r="F11" s="9">
         <v>25</v>
       </c>
-      <c r="G6" s="9"/>
-      <c r="H6" s="10"/>
+      <c r="G11" s="9">
+        <v>0</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="7" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:8">
-      <c r="B7" s="8">
-        <v>11003</v>
-      </c>
-      <c r="C7" s="8" t="s">
+    <row r="12" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:9">
+      <c r="B12" s="9">
+        <v>12003</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="9">
+        <v>10003</v>
+      </c>
+      <c r="E12" s="9">
+        <v>2</v>
+      </c>
+      <c r="F12" s="9">
+        <v>25</v>
+      </c>
+      <c r="G12" s="9">
+        <v>0</v>
+      </c>
+      <c r="H12" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="8">
+      <c r="I12" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:9">
+      <c r="B13" s="9">
+        <v>12004</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="9">
+        <v>10004</v>
+      </c>
+      <c r="E13" s="9">
+        <v>2</v>
+      </c>
+      <c r="F13" s="9">
+        <v>25</v>
+      </c>
+      <c r="G13" s="9">
+        <v>0</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:9">
+      <c r="B14" s="9">
+        <v>12005</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="9">
+        <v>10005</v>
+      </c>
+      <c r="E14" s="9">
+        <v>2</v>
+      </c>
+      <c r="F14" s="9">
+        <v>25</v>
+      </c>
+      <c r="G14" s="9">
+        <v>0</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:9">
+      <c r="B15" s="9">
+        <v>13001</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="9">
+        <v>10001</v>
+      </c>
+      <c r="E15" s="9">
+        <v>3</v>
+      </c>
+      <c r="F15" s="9">
+        <v>25</v>
+      </c>
+      <c r="G15" s="9">
+        <v>0</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I15" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:9">
+      <c r="B16" s="9">
+        <v>13002</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" s="9">
+        <v>10002</v>
+      </c>
+      <c r="E16" s="9">
+        <v>3</v>
+      </c>
+      <c r="F16" s="9">
+        <v>25</v>
+      </c>
+      <c r="G16" s="9">
+        <v>0</v>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I16" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:9">
+      <c r="B17" s="9">
+        <v>13003</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" s="9">
         <v>10003</v>
       </c>
-      <c r="E7" s="8">
-        <v>1</v>
-      </c>
-      <c r="F7" s="8">
+      <c r="E17" s="9">
+        <v>3</v>
+      </c>
+      <c r="F17" s="9">
         <v>25</v>
       </c>
-      <c r="G7" s="9"/>
-      <c r="H7" s="10"/>
+      <c r="G17" s="9">
+        <v>0</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I17" s="11" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="8" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:8">
-      <c r="B8" s="8">
-        <v>11004</v>
-      </c>
-      <c r="C8" s="8" t="s">
+    <row r="18" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:9">
+      <c r="B18" s="9">
+        <v>13004</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18" s="9">
+        <v>10004</v>
+      </c>
+      <c r="E18" s="9">
+        <v>3</v>
+      </c>
+      <c r="F18" s="9">
+        <v>25</v>
+      </c>
+      <c r="G18" s="9">
+        <v>0</v>
+      </c>
+      <c r="H18" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I18" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="8">
-        <v>10004</v>
-      </c>
-      <c r="E8" s="8">
-        <v>1</v>
-      </c>
-      <c r="F8" s="8">
+    </row>
+    <row r="19" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:9">
+      <c r="B19" s="9">
+        <v>13005</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" s="9">
+        <v>10005</v>
+      </c>
+      <c r="E19" s="9">
+        <v>3</v>
+      </c>
+      <c r="F19" s="9">
         <v>25</v>
       </c>
-      <c r="G8" s="9"/>
-      <c r="H8" s="10"/>
-    </row>
-    <row r="9" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:8">
-      <c r="B9" s="8">
-        <v>11005</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="8">
-        <v>10005</v>
-      </c>
-      <c r="E9" s="8">
-        <v>1</v>
-      </c>
-      <c r="F9" s="8">
-        <v>25</v>
-      </c>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-    </row>
-    <row r="10" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:8">
-      <c r="B10" s="8">
-        <v>12001</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="8">
-        <v>10001</v>
-      </c>
-      <c r="E10" s="8">
-        <v>2</v>
-      </c>
-      <c r="F10" s="8">
-        <v>25</v>
-      </c>
-      <c r="G10" s="9"/>
-      <c r="H10" s="10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:8">
-      <c r="B11" s="8">
-        <v>12002</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="8">
-        <v>10002</v>
-      </c>
-      <c r="E11" s="8">
-        <v>2</v>
-      </c>
-      <c r="F11" s="8">
-        <v>25</v>
-      </c>
-      <c r="G11" s="9"/>
-      <c r="H11" s="10"/>
-    </row>
-    <row r="12" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:8">
-      <c r="B12" s="8">
-        <v>12003</v>
-      </c>
-      <c r="C12" s="8" t="s">
+      <c r="G19" s="9">
+        <v>0</v>
+      </c>
+      <c r="H19" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="D12" s="8">
-        <v>10003</v>
-      </c>
-      <c r="E12" s="8">
-        <v>2</v>
-      </c>
-      <c r="F12" s="8">
-        <v>25</v>
-      </c>
-      <c r="G12" s="9"/>
-      <c r="H12" s="10"/>
-    </row>
-    <row r="13" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:8">
-      <c r="B13" s="8">
-        <v>12004</v>
-      </c>
-      <c r="C13" s="8" t="s">
+      <c r="I19" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="D13" s="8">
-        <v>10004</v>
-      </c>
-      <c r="E13" s="8">
-        <v>2</v>
-      </c>
-      <c r="F13" s="8">
-        <v>25</v>
-      </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="10"/>
-    </row>
-    <row r="14" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:8">
-      <c r="B14" s="8">
-        <v>12005</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D14" s="8">
-        <v>10005</v>
-      </c>
-      <c r="E14" s="8">
-        <v>2</v>
-      </c>
-      <c r="F14" s="8">
-        <v>25</v>
-      </c>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-    </row>
-    <row r="15" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:8">
-      <c r="B15" s="8">
-        <v>13001</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="8">
-        <v>10001</v>
-      </c>
-      <c r="E15" s="8">
-        <v>3</v>
-      </c>
-      <c r="F15" s="8">
-        <v>25</v>
-      </c>
-      <c r="G15" s="9"/>
-      <c r="H15" s="10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:8">
-      <c r="B16" s="8">
-        <v>13002</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D16" s="8">
-        <v>10002</v>
-      </c>
-      <c r="E16" s="8">
-        <v>3</v>
-      </c>
-      <c r="F16" s="8">
-        <v>25</v>
-      </c>
-      <c r="G16" s="9"/>
-      <c r="H16" s="10"/>
-    </row>
-    <row r="17" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:8">
-      <c r="B17" s="8">
-        <v>13003</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D17" s="8">
-        <v>10003</v>
-      </c>
-      <c r="E17" s="8">
-        <v>3</v>
-      </c>
-      <c r="F17" s="8">
-        <v>25</v>
-      </c>
-      <c r="G17" s="9"/>
-      <c r="H17" s="10"/>
-    </row>
-    <row r="18" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:8">
-      <c r="B18" s="8">
-        <v>13004</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D18" s="8">
-        <v>10004</v>
-      </c>
-      <c r="E18" s="8">
-        <v>3</v>
-      </c>
-      <c r="F18" s="8">
-        <v>25</v>
-      </c>
-      <c r="G18" s="9"/>
-      <c r="H18" s="10"/>
-    </row>
-    <row r="19" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:8">
-      <c r="B19" s="8">
-        <v>13005</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D19" s="8">
-        <v>10005</v>
-      </c>
-      <c r="E19" s="8">
-        <v>3</v>
-      </c>
-      <c r="F19" s="8">
-        <v>25</v>
-      </c>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Unity/Assets/Config/Excel/GemTalentConfig.xlsx
+++ b/Unity/Assets/Config/Excel/GemTalentConfig.xlsx
@@ -11723,7 +11723,7 @@
       </c>
       <c r="I2" s="5" t="inlineStr">
         <is>
-          <t>(list#sep=\#),(list#sep=@),PropEffect#sep=;</t>
+          <t>(list#sep=@),PropEffect#sep=;</t>
         </is>
       </c>
     </row>
